--- a/SINGLE HADITH CONTENT/missing_input/[V1] LULUWAL MARJAN-BANGLA_missing.xlsx
+++ b/SINGLE HADITH CONTENT/missing_input/[V1] LULUWAL MARJAN-BANGLA_missing.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1334,6 +1334,465 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>821</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>حديث أَنَسٍ، أَنَّ رَسُولَ اللهِ صَلَّى اللَّهُ عَلَيْهِ وَسَلَّمَ، لَمَّا حَلَقَ رَأْسَهُ، كَانَ أَبُو طَلْحَةَ أَوَّلَ مَنْ أَخَذَ مِنْ شَعَرِهِ</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>আল্লাহর রাসূল (صلى الله عليه وسلم) তাঁর মাথা মুণ্ডন করলে আবূ তলহা (রাঃ)-ই প্রথমে তাঁর চুল সংগ্রহ করেন।</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>822</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>حديث عَبْدِ اللهِ بْنِ عَمْرِو بْنِ الْعَاصِ، أَنَّ رَسُولَ اللهِ صَلَّى اللَّهُ عَلَيْهِ وَسَلَّمَ وَقَفَ فِي حَجَّةِ الْوَدَاعِ بِمِنًى لِلنَّاسِ يَسْأَلُونَهُ، فَجَاءَهُ رَجُلٌ، فَقَالَ: لَمْ أَشْعُرْ فَحَلَقْتُ قَبْلَ أَنْ أَذْبَحَ، فَقَالَ: اذْبَحْ وَلاَ حَرَجَ فَجَاءَ آخَرُ، فَقَالَ: لَمْ أَشْعُرْ فَنَحَرْتُ قَبْلَ أَنْ أَرْمِيَ قَالَ: ارْمِ وَلاَ حَرَجَ فَمَا سُئِلَ النَّبِيُّ صَلَّى اللَّهُ عَلَيْهِ وَسَلَّمَ عَنْ شَيْءٍ قُدِّمَ وَلاَ أُخِّرَ إِلاَّ قَالَ: افْعَلْ وَلاَ حَرَجَ</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>বিদায় হজ্জের সময় আল্লাহর রাসূল (صلى الله عليه وسلم) (সাওয়ারীতে) অবস্থান করছিলেন, তখন সাহাবীগণ তাঁকে জিজ্ঞেস করতে লাগলেনঃ একজন জিজ্ঞেস করলেন, আমি জানতাম না, তাই কুরবানী করার আগেই (মাথা) কামিয়ে ফেলেছি। তিনি ইরশাদ করলেনঃ তুমি কুরবানী করে নাও, কোন দোষ নেই। অতঃপর অপর একজন এসে বললেন, আমি না জেনে কঙ্কর মারার পূর্বেই কুরবানী করে ফেলেছি। তিনি ইরশাদ করলেনঃ কঙ্কর মেরে নাও, কোন দোষ নেই। সেদিন যে কোন কাজ আগে পিছে করা সম্পর্কে জিজ্ঞেস করা হলে তিনি বলেনঃ করে নাও, কোন দোষ নেই।</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>حديث ابْنِ عَبَّاسٍ، أَنَّ النَّبِيَّ صَلَّى اللَّهُ عَلَيْهِ وَسَلَّمَ قِيلَ لَهُ فِي الذَّبْحِ وَالْحَلْقِ وَالرَّمْيِ وَالتَّقْدِيمِ وَالتَّأْخِيرِ، فَقَالَ: لاَ حَرَجَ</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>নবী (صلى الله عليه وسلم)-কে যবহ করা, মাথা কামান ও কঙ্কর মারা এবং (এ কাজগুলো) আগে-পিছে করা সম্পর্কে জিজ্ঞাসা করা হলে তিনি বললেনঃ কোন দোষ নেই।</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>824</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>حديث أَنَسِ بْنِ مَالِكٍ عَنْ عَبْدِ العَزِيزِ بْنِ رُفَيْعٍ، قَالَ: سَأَلْتُ أَنَسَ بْنَ مَالِكٍ رضي الله عنه، قُلْتُ: أَخْبِرْنِي بِشَيْءٍ عَقَلْتَهُ عَنِ النَّبِيِّ صَلَّى اللَّهُ عَلَيْهِ وَسَلَّمَ، أَيْنَ صَلَّى الظُّهْرَ وَالْعَصْرَ يَوْمَ التَّرْوِيَةِ قَالَ: بِمِنًى قُلْتُ: فَأَيْنَ صَلَّى الْعَصْرَ يَوْمَ النَّفْرِ قَالَ: بِالأَبْطَحِ ثُمَّ قَالَ: افْعَلْ كَمَا يَفْعَلُ أُمَرَاؤُكَ</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>আমি আনাস ইব্‌নু মালিক (রাঃ)-কে জিজ্ঞেস করলাম, নবী (صلى الله عليه وسلم) সম্পর্কে আপনি যা উত্তমরূপে স্মরণ রেখেছেন তার কিছুটা বলুন। বলুন, যিলহাজ্জ মাসের আট তারিখে যুহর ও ‘আসরের সালাত তিনি কোথায় আদায় করতেন? তিনি বললেন, মিনায়। আমি বললাম, মিনা হতে ফিরার দিন ‘আসরের সালাত তিনি কোথায় আদায় করেছেন? তিনি বললেন, মুহাস্‌সাবে। এরপর আনাস (রাঃ) বললেন, তোমাদের আমীরগণ যেরূপ করবে, তোমরাও অনুরূপ কর।</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>حديث عَائِشَةَ، قَالَتْ: إِنَّمَا كَانَ مَنْزِلٌ يَنْزِلُهُ النَّبِيُّ صَلَّى اللَّهُ عَلَيْهِ وَسَلَّمَ لِيَكُونَ أَسْمَحَ لِخُرُوجِهِ، تَعْنِي بِالأَبْطَحِ</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>তা হল একটি মানযিল মাত্র, যেখানে নবী (صلى الله عليه وسلم) অবতরণ করতেন, যাতে বেরিয়ে যাওয়া সহজতর হয় অর্থাৎ এর দ্বারা আবতাহ বুঝানো হয়েছে।</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>826</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>حديث ابْنِ عَبَّاسٍ، قَالَ: لَيْسَ التَّحْصِيبُ بِشَيْءٍ، إِنَّمَا هُوَ مَنْزِلٌ نَزَلَهُ رَسُولُ اللهِ صَلَّى اللَّهُ عَلَيْهِ وَسَلَّمَ</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>মুহাস্‌সাবে অবতরণ করা (হজ্জের) কিছুই নয়। এ তো শুধু একটি মানযিল, যেখানে নবী (صلى الله عليه وسلم) অবতরণ করেছিলেন।</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>827</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>حديث أَبِي هُرَيْرَةَ رضي الله عنه، قَالَ: قَالَ النَّبِيُّ صَلَّى اللَّهُ عَلَيْهِ وَسَلَّمَ مِنَ الْغَدِ يَوْمَ النَّحْرِ وَهُوَ بِمِنًى: نَحْنُ نَازِلُونَ غَدًا بِخَيْفِ بَنِى كِنَانَةَ حَيْثُ تَقَاسَمُوا عَلَى الْكُفْرِ يَعْنِى ذلِكَ الْمُحَصَّبَ وَذلِكَ أَنَّ قُرَيْشًا وَكِنَانَةَ تَحَالَفَتْ عَلَى بَنِى هَاشِمٍ وَبَنِى عَبْدِ الْمُطَّلِبِ، أَوْ بَنِى الْمُطَّلِبِ، أَنْ لاَ يُنَاكِحُوهُمْ وَلاَ يُبَايِعُوهُمْ حَتَّى يُسْلِمُوا إِلَيْهِمُ النَّبِيَّ صَلَّى اللَّهُ عَلَيْهِ وَسَلَّمَ</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>কুরবানীর দিনে মিনায় অবস্থানকালে নবী (صلى الله عليه وسلم) বললেনঃ আমরা আগামীকাল (ইনশাআল্লাহ) খায়ফে বনী কিনানায় অবতরণ করব, যেখানে তারা কুফরীর উপরে শপথ নিয়েছিল। (রাবী বলেন) খায়ফ বনী কিনানাই হলো মুহাস্‌সাব। কুরায়শ ও কিনানা গোত্র বনূ হাশিম ও বনূ আবদুল মুত্তালিব-এর বিরুদ্ধে এ বিষয়ে চুক্তিবদ্ধ হয়েছিল, যে পর্যন্ত নবী (صلى الله عليه وسلم)-কে তাদের হাতে সমর্পণ না করবে সে পর্যন্ত তাদের সাথে বিয়ে-শাদী ও বেচা-কেনা বন্ধ থাকবে।</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>828</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>حديث عَبْدِ اللهِ بْنِ عُمَرَ، قَالَ: اسْتَأْذَنَ الْعَبَّاسُ بْنُ عَبْدِ الْمُطَّلِبِ رضي الله عنه رَسُولَ اللهِ صَلَّى اللَّهُ عَلَيْهِ وَسَلَّمَ أَنْ يَبِيتَ بِمَكَّةَ لَيَالِيَ مِنًى مِنْ أَجْلِ سِقَايَتِهِ، فَأَذِنَ لَهُ</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>তিনি বলেন, ‘আব্বাস ইব্‌নু ‘আবদুল মুত্তালিব (রাঃ) আল্লাহর রাসূল (صلى الله عليه وسلم)-এর নিকট হাজীদের পানি পান করানোর উদ্দেশে মিনায় অবস্থানের রাতগুলো মাক্কায় কাটানোর অনুমতি চাইলে তিনি তাঁকে অনুমতি দেন।</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>829</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>حديث عَلِيٍّ رضي الله عنه، أَنَّ النَّبِيَّ صَلَّى اللَّهُ عَلَيْهِ وَسَلَّمَ أَمَرَهُ أَنْ يَقُومَ عَلَى بُدْنِهِ، وَأَنْ يَقْسِمَ بُدْنَهُ كُلَّهَا لُحُومَهَا وَجُلُودَهَا وَجِلاَلَهَا وَلاَ يُعْطِيَ فِي جِزَارَتِهَا شَيْئًا</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>তাঁকে নবী (صلى الله عليه وسلم) তাঁর নিজের কুরবানীর জানোয়ারের পাশে দাঁড়াতে আর এগুলোর সমুদয় গোশ্‌ত, চামড়া এবং পিঠের আবরণসমূহ বিতরণ করতে নির্দেশ দেন এবং তা হতে যেন কসাইকে পারিশ্রমিক হিসেবে কিছুই না দেয়া হয়।</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>830</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>حديث ابْنِ عُمَرَ (أَنَّهُ) أَتَى عَلَى رَجُلٍ قَدْ أَنَاخَ بَدَنَتَهُ يَنْحَرُهَا، قَالَ: ابْعَثْهَا قِيَامًا مُقَيَّدَةً سُنَّةَ مُحَمَّدٍ صَلَّى اللَّهُ عَلَيْهِ وَسَلَّمَ</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>আমি ইব্‌নু ‘উমার (রাঃ)-কে দেখেছি যে, তিনি আসলেন এমন এক ব্যক্তির নিকট, যে তার নিজের উটটিকে নহর করার জন্য বসিয়ে রেখেছিল। ইব্‌নু ‘উমার (রাঃ) বললেন, সেটি উঠিয়ে দাঁড়ানো অবস্থায় বেঁধে নাও। (এটা) মুহাম্মদ (صلى الله عليه وسلم)-এর সুন্নাত।</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>831</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>حديث عَائِشَةَ، قَالَتْ: فَتَلْتُ قَلاَئِدَ بُدْنِ النَّبِيِّ صَلَّى اللَّهُ عَلَيْهِ وَسَلَّمَ، بِيَدَيَّ، ثُمَّ قَلَّدَهَا وَأَشْعَرَهَا وَأَهْدَاهَا؛ فَمَا حَرُمَ عَلَيْهِ شَيْءٌ كَانَ أُحِلَّ لَهُ</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>আমি নিজ হাতে নবী (صلى الله عليه وسلم)-এর কুরবানীর পশুর কিলাদা পাকিয়ে দিয়েছি। এরপর তিনি তাকে কিলাদা পরিয়ে ইশ‘আর করার পর পাঠিয়ে দিয়েছেন এবং তাঁর জন্য যা হালাল ছিল এতে তা হারাম হয়নি।</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>832</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>حديث عَائِشَةَ أَنَّ زِيَادَ بْنَ أَبِي سُفْيَانَ كَتَبَ إِلَى عَائِشَةَ، إِنَّ عَبْدَ اللهِ بْنَ عَبَّاسٍ، قَالَ: مَنْ أَهْدَى هَدْيًا حَرُمَ عَلَيْهِ مَا يَحْرُمُ عَلَى الْحَاجِّ حَتَّى يُنْحَرَ هَدْيُهُ فَقَالَتْ عَائِشَةُ: لَيْسَ كَمَا قَالَ ابْنُ عَبَّاسٍ؛ أَنَا فَتَلْتُ قَلاَئِدَ هَدْيِ رَسُولِ اللهِ صَلَّى اللَّهُ عَلَيْهِ وَسَلَّمَ بِيَدَيَّ ثُمَّ قَلَّدَهَا رَسُولُ اللهِ صَلَّى اللَّهُ عَلَيْهِ وَسَلَّمَ، بِيَدَيْهِ، ثُمَّ بَعَثَ بِهَا مَعَ أَبِي، فَلَمْ يَحْرُمْ عَلَى رَسُولِ اللهِ صَلَّى اللَّهُ عَلَيْهِ وَسَلَّمَ، شَيْءٌ أَحَلَّهُ اللهُ حَتَّى نُحِرَ الْهَدْيُ</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>তিনি ‘আয়িশাহ্ (রাঃ)-এর নিকট পত্র লিখলেন যে, ‘আবদুল্লাহ ইব্‌নু ‘আব্বাস (রাঃ) বলেছেন, যে ব্যক্তি কুরবানীর পশু (মাক্কাহ্) পাঠায় তা যবহ না করা পর্যন্ত তার জন্য ঐ সমস্ত কাজ হারাম হয়ে যায়, যা হাজীদের জন্য হারাম। (বর্ণনাকারিণী) আমরাহ (রহ.) বলেন, ‘আয়িশাহ্ (রাঃ) বললেন, ইব্‌নু ‘আব্বাস (রাঃ) যেমন বলেছেন, ব্যাপার তেমন নয়। আমি নিজ হাতে আল্লাহর রাসূল (صلى الله عليه وسلم)-এর কুরবানীর পশুর কিলাদা পাকিয়ে দিয়েছি আর তিনি নিজ হাতে তাকে কিলাদাহ পরিয়ে দেন। এরপর আমার পিতার সঙ্গে তা পাঠান। সে জানোয়ার যবহ করা পর্যন্ত আল্লাহ কর্তৃক হালাল করা কোন বস্তুই আল্লাহর রাসূল (صلى الله عليه وسلم)-এর প্রতি হারাম হয়নি।</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>833</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>حديث أَبِي هُرَيْرَةَ رضي الله عنه، أَنَّ رَسُولَ اللهِ صَلَّى اللَّهُ عَلَيْهِ وَسَلَّمَ رَأَى رَجُلاً يَسُوقُ بَدَنَةً، فَقَالَ: ارْكَبْهَا فَقَالَ: إِنَّهَا بَدَنَةٌ فَقَالَ: ارْكَبْهَا قَالَ: إِنَّهَا بَدَنَةٌ قَالَ: ارْكَبْهَا وَيْلَكَ فِي الثَّالِثَةِ أَوْ فِي الثَّانِيَةِ</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>আল্লাহর রাসূল (صلى الله عليه وسلم) এক ব্যক্তিকে কুরবানীর উট হাঁকিয়ে নিতে দেখে বললেন, এর পিঠে আরোহণ কর। সে বলল, এ তো কুরবানীর উট। আল্লাহর রাসূল (صلى الله عليه وسلم) বললেন, এর পিঠে সওয়ার হয়ে চল। এবারও লোকটি বলল, এ-তো কুরবানীর উট। এরপরও আল্লাহর রাসূল (صلى الله عليه وسلم) বললেন, এর পিঠে আরোহণ কর, তোমার সর্বনাশ! এ কথাটি দ্বিতীয় বা তৃতীয়বারে বলেছেন।</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>834</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>حديث أَنَسٍ رضي الله عنه، أَنَّ النَّبِيَّ صَلَّى اللَّهُ عَلَيْهِ وَسَلَّمَ، رَأَى رَجُلاً يَسُوقُ بَدَنَةً، فَقَالَ: ارْكَبْهَا قَالَ: إِنَّهَا بَدَنَةٌ، قَالَ: ارْكَبْهَا، قَالَ: إِنَّهَا بَدَنَةٌ قَالَ: ارْكَبْهَا ثَلاَثًا</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>নবী (صلى الله عليه وسلم) এক ব্যক্তিকে কুরবানীর উট হাঁকিয়ে নিতে দেখে বললেন, এর উপর সওয়ার হয়ে যাও। সে বলল, এ তো কুরবানীর উট। তিনি বললেন, এর উপর সওয়ার হয়ে যাও। লোকটি বলল, এ তো কুরবানীর উট। তিনি বললেন, এর উপর সওয়ার হয়ে যাও। এ কথাটি তিনি তিনবার বললেন।</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>835</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>حديث ابْنِ عَبَّاسٍ، قَالَ: أُمِرَ النَّاسُ أَنْ يَكُونَ آخِرُ عَهْدِهِمْ بِالْبَيْتِ، إِلاَّ أَنَّهُ خُفِّفَ عَنِ الْحَائِضِ</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>লোকেদের আদেশ দেয়া হয় যে, তাদের শেষ কাজ যেন হয় বাইতুল্লাহর তাওয়াফ। তবে এ হুকুম ঋতুবতী মহিলাদের জন্য শিথিল করা হয়েছে।</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>حديث عَائِشَةَ، زَوْجِ النَّبِيِّ صَلَّى اللَّهُ عَلَيْهِ وَسَلَّمَ، أَنَّهَا قَالَتْ لِرَسُولِ اللهِ صَلَّى اللَّهُ عَلَيْهِ وَسَلَّمَ: يَا رَسُولَ اللهِ إِنَّ صَفِيَّةَ بِنْتَ حُيَيٍّ قَدْ حَاضَتْ قَالَ رَسُولُ اللهِ صَلَّى اللَّهُ عَلَيْهِ وَسَلَّمَ: لَعَلَّهَا تَحْبِسُنَا، [ص: 70] أَلَمْ تَكُنْ طَافَتْ مَعَكُنَّ فَقَالُوا: بَلَى؛ قَالَ: فَاخْرُجِي</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>তিনি আল্লাহর রাসূল (صلى الله عليه وسلم)-কে জিজ্ঞেস করলেনঃ হে আল্লাহ্‌র রাসূল! সাফিয়্যাহ বিনতু হুয়াইয়ের হায়য শুরু হয়েছে। তিনি বললেনঃ সে তো আমাদেরকে আটকে রাখবে। সে কি তোমাদের সঙ্গে তাওয়াফে-যিয়ারত করেনি? তাঁরা জবাব দিলেন, হাঁ করেছেন। তিনি বললেনঃ তা হলে বের হও।</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>837</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>حديث عَائِشَةَ، قَالَتْ: حَاضَتْ صَفِيَّةُ لَيْلَةَ النَّفْرِ، فَقَالَتْ: مَا أُرَانِي إِلاَّ حَابِسَتَكُمْ؛ قَالَ النَّبِيُّ صَلَّى اللَّهُ عَلَيْهِ وَسَلَّمَ: عَقْرَى حَلْقَى أَطَافَتْ يَوْمَ النَّحْرِ قِيلَ: نَعَمْ قَالَ: فَانْفِرِى</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>প্রত্যাবর্তনের রাত এলে সাফিয়্যাহ বিন্‌তু হুয়াই (রাঃ)-এর ঋতু আরম্ভ হলে তিনি বললেন, আমার ধারণা, আমি তোমাদের আটকে ফেললাম। নবী (صلى الله عليه وسلم) তা শুনে ‘আকরা’ ‘হালকা’ বলে বিরক্তি প্রকাশ করে বললেনঃ তুমি কি কুরবানীর দিন তাওয়াফ করেছিলে? সাফিয়্যাহ (রাঃ) বললেন, হাঁ। তখন নবী (صلى الله عليه وسلم) বললেনঃ তবে চল।</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>838</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>حديث بِلاَلٍ عَنْ عَبْدِ اللهِ بْنِ عُمَرَ، أَنَّ رَسُولَ اللهِ صَلَّى اللَّهُ عَلَيْهِ وَسَلَّمَ دَخَلَ الْكَعْبَةَ، وَأُسَامَةُ بْنُ زَيْدٍ وَبِلاَلٌ وَعُثْمَانُ بْنُ طَلْحَةَ الْحَجَبِيُّ، فَأَغْلَقَهَا عَلَيْهِ، وَمَكُثَ فِيهَا [ص: 71] فَسَأَلْتُ بِلاَلاً حِينَ خَرَجَ: مَا صَنَعَ النَّبِيُّ صَلَّى اللَّهُ عَلَيْهِ وَسَلَّمَ قَالَ: جَعَلَ عَمُودًا عَنْ يَسَارِهِ وَعَمُودًا عَنْ يَمِينِهِ، وَثَلاَثَةَ أَعْمِدَةٍ وَرَاءَهُ، وَكَانَ الْبَيْتُ يَوْمَئِذٍ عَلَى سِتَّةِ أَعْمِدَةٍ، ثُمَّ صَلَّى</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>আল্লাহর রাসূল (صلى الله عليه وسلم) আর উসামা ইব্‌নু যায়দ, বিলাল এবং ‘উসমান ইব্‌নু তালহা হাজাবী (রাঃ) কাবায় প্রবেশ করলেন। নবী (صلى الله عليه وسلم)-এর প্রবেশের সাথে সাথে ‘উসমান (রাঃ) কাবার দরজা বন্ধ করে দিলেন। তাঁরা কিছুক্ষণ ভিতরে ছিলেন। বিলাল (রাঃ) বের হলে আমি তাঁকে বললামঃ নবী (صلى الله عليه وسلم) কী করলেন? তিনি বললেনঃ একটা খুঁটি বাম দিকে, একটা খুঁটি ডান দিকে আর তিনটা খুঁটি পেছনে রাখলেন। আর তখন বায়তুল্লাহ ছিল ছয়টি খুঁটিবিশিষ্ট। অতঃপর তিনি সালাত আদায় করলেন।</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>839</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>حديث ابْنِ عَبَّاسٍ، قَالَ: لَمَّا دَخَلَ النَّبِيُّ صَلَّى اللَّهُ عَلَيْهِ وَسَلَّمَ الْبَيْتَ دَعَا فِي نَوَاحِيهِ كُلِّهَا وَلَمْ يُصَلِّ حَتَّى خَرَجَ مِنْهُ؛ فَلَمَّا خَرَجَ رَكَعَ رَكْعَتَيْنِ فِي قِبَلِ الْكَعْبَةِ، وَقَالَ: هذِهِ الْقِبْلَةُ</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>যখন নবী (صلى الله عليه وسلم) কাবায় প্রবেশ করেন, তখন তার সকল দিকে দু‘আ করেছেন, সালাত আদায় না করেই বেরিয়ে এসেছেন এবং বের হবার পর কাবার সামনে দুইরাক‘আত সালাত আদায় করেছেন, এবং বলেছেন, এটাই কেবলা।</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>840</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>حديث عَبْدِ اللهِ بْنِ أَبِي أَوْفَى، قَالَ: اعْتَمَرَ رَسُولُ اللهِ صَلَّى اللَّهُ عَلَيْهِ وَسَلَّمَ، فَطَافَ بِالْبَيْتِ وَصَلَّى خَلْفَ الْمَقَامِ رَكْعَتَيْنِ وَمَعَهُ مَنْ يَسْتُرُهُ مِنَ النَّاسِ فَقَالَ لَهُ رَجُلٌ: أَدَخَلَ رَسُولُ اللهِ صَلَّى اللَّهُ عَلَيْهِ وَسَلَّمَ الْكَعْبَةَ قَالَ: لاَ</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>আল্লাহর রাসূল (صلى الله عليه وسلم) ‘উমরাহ করতে গিয়ে বাইতুল্লাহ তাওয়াফ করলেন ও মাকামে ইবরাহীমের পিছনে দুই রাক‘আত সালাত আদায় করলেন এবং তাঁর সাথে এ সকল সাহাবী ছিলেন যারা তাঁকে লোকদের হতে আড়াল করে ছিলেন। আল্লাহর রাসূল (صلى الله عليه وسلم) কাবার ভিতরে প্রবেশ করেছিলেন কি-না- এক ব্যক্তি আবূ আওফা (রাঃ)-এর নিকট তা জিজ্ঞেস করলে তিনি বললেন, না।</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>852</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>حديث عَبْدِ اللهِ بْنِ عُمَرَ، أَنَّ رَسُولَ اللهِ صَلَّى اللَّهُ عَلَيْهِ وَسَلَّمَ أَنَاخَ بِالْبَطْحَاءِ بِذِي الْحُلَيْفَةِ فَصَلَّى بِهَا وَكَانَ عَبْدُ اللهِ بْنُ عُمَرَ، يَفْعَلُ ذلِكَ</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>আল্লাহর রাসূল (صلى الله عليه وسلم) যুল-হুলাইফার বাত্হা নামক উপত্যকায় উট বসিয়ে সালাত আদায় করেন। (রাবী নাফি‘ বলেন) ইব্‌নু ‘উমার (রাঃ)-ও তাই করতেন।</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>853</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>حديث عَبْدِ اللهِ بْنِ عُمَرَ، عَنِ النَّبِيِّ صَلَّى اللَّهُ عَلَيْهِ وَسَلَّمَ، أَنَّهُ رُئِيَ وَهُوَ فِي مُعَرَّسٍ بِذِي الْحُلَيْفَةِ بِبَطْنِ الْوَادِي، قِيلَ لَهُ إِنَّكَ بِبَطْحَاءَ مُبَارَكَة (قَالَ مُوسى بْنُ عُقْبَةَ، أَحَدُ رِجَالِ السَّنَدِ) : وَقَدْ أَنَاخَ بِنَا سَالِمٌ يَتَوَخَّى بِالْمُنَاخِ الَّذِي كَانَ عَبْدُ اللهِ يُنِيخُ، يَتَحَرَّى مُعَرَّسَ رَسُولِ اللهِ صَلَّى اللَّهُ عَلَيْهِ وَسَلَّمَ، وَهُوَ أَسْفَلُ مِنَ الْمَسْجِدِ الَّذِي بِبَطْنِ الْوَادِي، بَيْنَهُمْ وَبَيْنَ الطَّرِيقِ وَسَطٌ مِنْ ذلِكَ</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>যুল-হুলাইফাহ (‘আকীক) উপত্যকায় রাত যাপনকালে তাঁকে স্বপ্নযোগে বলা হয়, আপনি বরকতময় উপত্যকায় অবস্থান করছেন। [রাবী মূসা ইব্‌নু ‘উকবাহ (রহ.) বলেন] সালিম (রহ.) আমাদেরকে সাথে নিয়ে উট বসিয়ে ঐ উট বসাবার স্থানটির খোঁজ করেন, যেখানে ‘আবদুল্লাহ ইব্‌নু ‘উমার (রাঃ) উট বসিয়ে আল্লাহর রাসূল (صلى الله عليه وسلم)-এর রাত যাপনের স্থানটি খোঁজ করতেন। সে স্থানটি উপত্যকায় মসজিদের নীচু জায়গায় অবতরণকারীদের ও রাস্তার একেবারে মধ্যবর্তী স্থানে অবস্থিত।</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>854</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>حديث أَبِي بَكْرٍ الصِّدِّيقِ رضي الله عنه، عَنْ أَبِي هُرَيْرَةَ، أَن أَبَا بَكْرٍ الصِّدِّيقَ رضي الله عنه، بَعَثَهُ فِي الْحَجَّةِ الَّتِي أَمَّرَهُ عَلَيْهَا رَسُولُ اللهِ صَلَّى اللَّهُ عَلَيْهِ وَسَلَّمَ، قَبْلَ حَجَّةِ الْوَدَاعِ يَوْمَ النَّحْرِ، فِي رَهْطٍ، يُؤَذِّنُ فِي النَّاسِ: أَلاَ لاَ يَحُجُّ بَعْدَ الْعَامِ مُشْرِكٌ، وَلاَ يَطُوفُ بِالْبَيْتِ عُرْيَانٌ</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>তিনি বলেন, বিদায় হাজ্জের পূর্বে যে হজ্জে আল্লাহর রাসূল (صلى الله عليه وسلم) আবূ বকর (রাঃ)-কে আমীর নিযুক্ত করেন, সে হজ্জে কুরবানীর দিন [আবূ বকর (রাঃ)] আমাকে একদল লোকের সঙ্গে পাঠালেন, যারা লোকদের কাছে ঘোষণা করবে যে, এ বছরের পর হতে কোন মুশরিক হজ্জ করবে না এবং উলঙ্গ হয়ে বায়তুল্লাহর তাওয়াফ করবে না।</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>855</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>حديث أَبِي هُرَيْرَةَ رضي الله عنه، أَنَّ رَسُولَ اللهِ صَلَّى اللَّهُ عَلَيْهِ وَسَلَّمَ، قَالَ: الْعُمْرَةُ إِلَى الْعُمْرَةِ كَفَّارَةٌ لِمَا بَيْنَهُمَا، وَالْحَجُّ الْمَبْرُورُ لَيْسَ لَهُ جَزَاءٌ إِلاَّ الْجَنَّةُ</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>আল্লাহর রাসূল (صلى الله عليه وسلم) বলেছেনঃ এক ‘উমরাহ’র পর আর এক ‘উমরাহ উভয়ের মধ্যবর্তী সময়ের (গুনাহের) জন্য কাফফারা। আর জান্নাতই হলো হজ্জে মাবরূরের প্রতিদান।</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>856</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>حديث أَبِي هُرَيْرَةَ رضي الله عنه، قَالَ: قَالَ رَسُولُ اللهِ صَلَّى اللَّهُ عَلَيْهِ وَسَلَّمَ: مَنْ حَجَّ هذَا الْبَيْتَ فَلَمْ يَرْفُثْ وَلَمْ يَفْسُقْ رَجَعَ كَمَا وَلَدَتْهُ أُمُّهُ</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>আল্লাহর রাসূল (صلى الله عليه وسلم) বলেছেন, যে ব্যক্তি এ ঘরের হাজ্জ আদায় করল এবং স্ত্রী সহবাস করল না এবং অন্যায় আচরণ করল না, সে প্রত্যাবর্তন করবে মাতৃগর্ভ হতে সদ্য প্রসূত শিশুর মত হয়ে।</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>858</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>حديث العَلاَءِ بْنِ الْحَضْرَمِيِّ، قَالَ: قَالَ رَسُولُ اللهِ صَلَّى اللَّهُ عَلَيْهِ وَسَلَّمَ: ثَلاَثٌ لِلْمُهَاجِرِ بَعْدَ الصَّدَرِ</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>আমি রাসূলুল্লাহ্ (صلى الله عليه وسلم) বলেছেন, মুহাজিরদের জন্য তাওয়াফে সদর* আদায় করার পর তিন দিন মাক্কায় থাকার অনুমতি আছে।*</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>859</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>حديث ابْنِ عَبَّاسٍ، قَالَ: قَالَ النَّبِيُّ صَلَّى اللَّهُ عَلَيْهِ وَسَلَّمَ، يَوْمَ افْتَتَحَ مَكَّةَ: لاَ هِجْرَةَ [ص: 78] وَلكِنْ جِهَادٌ وَنِيَّةٌ، وَإِذَا اسْتُنْفِرْتُمْ فَانْفِرُوا، فَإِنَّ هذَا بَلَدٌ حَرَّمَ اللهُ يَوْمَ خَلَقَ السَّموَاتِ وَالأَرْضَ، وَهُوَ حَرَامٌ بِحُرْمَةِ اللهِ إِلَى يَوْمِ الْقِيَامَةِ، وَإِنَّهُ لَمْ يَحِلَّ الْقِتَالُ فِيهِ َلأحَدٍ قَبْلِى، وَلَمْ يَحِلَّ لِي إِلاَّ سَاعَةً مِنْ نَهَارٍ، فَهُوَ حَرَامٌ بِحُرْمَةِ اللهِ إِلَى يَوْمِ الْقِيَامَةِ، لاَ يُعْضَدُ شَوْكُهُ، وَلاَ يُنَفَّرُ صَيْدُهُ، وَلاَ يَلْتَقِطُ لُقَطَتَهُ إِلاَّ مَنْ عَرَّفَهَا، وَلاَ يُخْتَلَى خَلاَهَا قَالَ الْعَبَّاسُ: يَا رَسُولَ اللهِ إِلاَّ الإِذْخِرَ فَإِنَّهُ لِقَيْنِهِمْ وَلِبُيُوتِهِمْ قَالَ: قَالَ: إِلاَّ الإِذْخِرَ</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>মাক্কাহ বিজয়ের দিন নবী (صلى الله عليه وسلم) বলেছিলেনঃ এখন হতে আর হিজরত নেই, রয়েছে কেবল জিহাদ এবং নিয়ত। সুতরাং যখন তোমাদেরকে জিহাদের জন্য ডাকা হবে, এ ডাকে তোমরা সাড়া দিবে। আসমান-যমীন সৃষ্টির দিন হতেই আল্লাহ তা‘আলা এ শহরকে হারম (মহাসম্মানিত) করে দিয়েছেন। আল্লাহ কর্তৃক সম্মানিত করার কারণেই কিয়ামাত পর্যন্ত এ শহর থাকবে মহাসম্মানিত হিসেবে। এ শহরে লড়াই করা আমার পূর্বেও কারো জন্য বৈধ ছিল না এবং আমার জন্যও দিনের কিছু অংশ ব্যতীত বৈধ হয়নি। আল্লাহ কর্তৃক সম্মানিত করার কারণে তা থাকবে কিয়ামাত পর্যন্ত মহাসম্মানিত হিসেবে। এর কাঁটা উপড়ে ফেলা যাবে না, তাড়ানো যাবে না এর শিকার্য জানোয়ারকে, ঘোষণা করার উদ্দেশ্য ব্যতীত কেউ এ স্থানে পড়ে থাকা কোন বস্তুকে উঠিয়ে নিতে পারবে না এবং কর্তন করা যাবে না এখানকার কাঁচা ঘাস ও তরুলতাগুলোকে। ‘আব্বাস (রাঃ) বললেন, হে আল্লাহর রাসূল! ইযখির বাদ দিয়ে। কেননা এ তো তাদের কর্মকারদের জন্য এবং তাদের ঘরে ব্যবহারের জন্য। বর্ণনাকারী বলেন, নবী (صلى الله عليه وسلم) বললেনঃ হাঁ, ইযখির বাদ দিয়ে।</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
